--- a/论文处理信息登记表.xlsx
+++ b/论文处理信息登记表.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\Date Record\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AFD3C82-57B9-4A52-A120-65F4327372EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FF1BB54-AC4B-4650-9D34-5B58773B3BA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="25">
   <si>
     <t>Paper 数据登记表</t>
   </si>
@@ -77,6 +77,12 @@
     <t>含 PT 数据</t>
   </si>
   <si>
+    <t>已复审</t>
+  </si>
+  <si>
+    <t>Aucone_AUG_PPCF_2024</t>
+  </si>
+  <si>
     <t>是</t>
   </si>
   <si>
@@ -86,22 +92,29 @@
     <t>待复审</t>
   </si>
   <si>
-    <t>已复审</t>
-  </si>
-  <si>
     <t>王澔博</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>Aucone_AUG_PPCF_2024</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Moret_TCV_PRL_1997</t>
+  </si>
+  <si>
+    <t>Merlo_TOKAMAK_PoP_2023</t>
+  </si>
+  <si>
+    <t>Muscente_TCV_NME_2023</t>
+  </si>
+  <si>
+    <t>Nishimura_DIIID_PoP_2020</t>
+  </si>
+  <si>
+    <t>Bagnato_TCV_PPCF_2024</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -155,6 +168,27 @@
       <sz val="9"/>
       <name val="宋体"/>
       <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F2937"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -287,33 +321,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="10" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -348,6 +361,30 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -516,125 +553,227 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="10" customWidth="1"/>
-    <col min="5" max="7" width="12" customWidth="1"/>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="28.25" customWidth="1"/>
+    <col min="3" max="3" width="28.08203125" customWidth="1"/>
+    <col min="4" max="4" width="22.33203125" customWidth="1"/>
+    <col min="5" max="6" width="20.58203125" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="4" customWidth="1"/>
     <col min="9" max="9" width="14" customWidth="1"/>
     <col min="10" max="10" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="16" customHeight="1">
-      <c r="A1" s="16" t="s">
+    <row r="1" spans="1:10" ht="10.65" customHeight="1">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="I1" s="19" t="s">
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="I1" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="J1" s="20"/>
-    </row>
-    <row r="2" spans="1:10" ht="14.65" customHeight="1">
-      <c r="A2" s="17" t="s">
+      <c r="J1" s="13"/>
+    </row>
+    <row r="2" spans="1:10" ht="9.75" customHeight="1">
+      <c r="A2" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="I2" s="10" t="s">
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="I2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J2" s="13">
-        <f>COUNTIF($A$5:$A$500,"&lt;&gt;")</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="14.65" customHeight="1">
-      <c r="A3" s="18" t="s">
+      <c r="J2" s="6">
+        <f>COUNTA(A5:A200)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="9.75" customHeight="1">
+      <c r="A3" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="18"/>
-      <c r="C3" s="18"/>
-      <c r="D3" s="18"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="18"/>
-      <c r="I3" s="11" t="s">
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
+      <c r="I3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="J3" s="14">
-        <f>COUNTIF($B$5:$B$500,"是")</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="14.65" customHeight="1">
-      <c r="A4" s="1" t="s">
+      <c r="J3" s="7">
+        <f>COUNTIF(B5:B200,"是")</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="32.5" customHeight="1">
+      <c r="A4" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="I4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="J4" s="14">
-        <f>COUNTIF($C$5:$C$500,"是")</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="14.65" customHeight="1">
-      <c r="A5" s="4" t="s">
+      <c r="J4" s="7">
+        <f>COUNTIF(C5:C200,"是")</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="32.5" customHeight="1">
+      <c r="A5" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="G5" s="2"/>
+      <c r="I5" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="F5" s="5" t="s">
+      <c r="J5" s="8">
+        <f>COUNTIF(D5:D200,"是")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="32.5" customHeight="1">
+      <c r="A6" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="G5" s="6"/>
-      <c r="I5" s="12" t="s">
+      <c r="F6" s="21" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="32.5" customHeight="1">
+      <c r="A7" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="J5" s="15">
-        <f>COUNTIF($D$5:$D$500,"是")</f>
-        <v>0</v>
+      <c r="E7" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" s="21" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="32.5" customHeight="1">
+      <c r="A8" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="F8" s="21" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="32.5" customHeight="1">
+      <c r="A9" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="F9" s="21" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="32.5" customHeight="1">
+      <c r="A10" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="E10" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" s="21" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -649,7 +788,7 @@
     <dataValidation type="list" sqref="B5:D5" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"是,否"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="E5" xr:uid="{00000000-0002-0000-0000-000003000000}">
+    <dataValidation type="list" sqref="E5" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"通过,待补充,待复审"</formula1>
     </dataValidation>
   </dataValidations>

--- a/论文处理信息登记表.xlsx
+++ b/论文处理信息登记表.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\Date Record\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FF1BB54-AC4B-4650-9D34-5B58773B3BA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{159BD360-FDCE-44BB-8C32-1994D3DCB001}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="30">
   <si>
     <t>Paper 数据登记表</t>
   </si>
@@ -108,6 +108,26 @@
   </si>
   <si>
     <t>Bagnato_TCV_PPCF_2024</t>
+  </si>
+  <si>
+    <t>Merlo_TCV_PoP_2019</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>是</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>否</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>待复审</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>王澔博</t>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -347,6 +367,30 @@
     <xf numFmtId="0" fontId="5" fillId="10" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -361,30 +405,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -553,7 +573,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
@@ -568,73 +588,73 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="10.65" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="I1" s="12" t="s">
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="I1" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="J1" s="13"/>
+      <c r="J1" s="21"/>
     </row>
     <row r="2" spans="1:10" ht="9.75" customHeight="1">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
       <c r="I2" s="3" t="s">
         <v>3</v>
       </c>
       <c r="J2" s="6">
         <f>COUNTA(A5:A200)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="9.75" customHeight="1">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11"/>
+      <c r="B3" s="19"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="19"/>
       <c r="I3" s="4" t="s">
         <v>5</v>
       </c>
       <c r="J3" s="7">
         <f>COUNTIF(B5:B200,"是")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="32.5" customHeight="1">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="D4" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="15" t="s">
+      <c r="E4" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="15" t="s">
+      <c r="F4" s="10" t="s">
         <v>11</v>
       </c>
       <c r="G4" s="1" t="s">
@@ -645,26 +665,26 @@
       </c>
       <c r="J4" s="7">
         <f>COUNTIF(C5:C200,"是")</f>
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="32.5" customHeight="1">
-      <c r="A5" s="16" t="s">
+      <c r="A5" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" s="18" t="s">
+      <c r="B5" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="E5" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="20" t="s">
+      <c r="F5" s="15" t="s">
         <v>19</v>
       </c>
       <c r="G5" s="2"/>
@@ -677,103 +697,123 @@
       </c>
     </row>
     <row r="6" spans="1:10" ht="32.5" customHeight="1">
-      <c r="A6" s="21" t="s">
+      <c r="A6" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="21" t="s">
+      <c r="B6" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="21" t="s">
+      <c r="C6" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="21" t="s">
+      <c r="E6" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="F6" s="21" t="s">
+      <c r="F6" s="16" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="32.5" customHeight="1">
-      <c r="A7" s="21" t="s">
+      <c r="A7" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="21" t="s">
+      <c r="B7" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="E7" s="21" t="s">
+      <c r="E7" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="21" t="s">
+      <c r="F7" s="16" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="32.5" customHeight="1">
-      <c r="A8" s="21" t="s">
+      <c r="A8" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" s="21" t="s">
+      <c r="B8" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="E8" s="21" t="s">
+      <c r="E8" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="F8" s="21" t="s">
+      <c r="F8" s="16" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="32.5" customHeight="1">
-      <c r="A9" s="21" t="s">
+      <c r="A9" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="D9" s="21" t="s">
+      <c r="B9" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="E9" s="21" t="s">
+      <c r="E9" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="F9" s="21" t="s">
+      <c r="F9" s="16" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="32.5" customHeight="1">
-      <c r="A10" s="21" t="s">
+      <c r="A10" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="B10" s="21" t="s">
+      <c r="B10" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="D10" s="21" t="s">
+      <c r="C10" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="E10" s="21" t="s">
+      <c r="E10" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="F10" s="21" t="s">
+      <c r="F10" s="16" t="s">
         <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="16.5">
+      <c r="A11" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="E11" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="F11" s="16" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/论文处理信息登记表.xlsx
+++ b/论文处理信息登记表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\Date Record\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{159BD360-FDCE-44BB-8C32-1994D3DCB001}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B397113F-4213-42A2-B6FB-D93127EAE899}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="33">
   <si>
     <t>Paper 数据登记表</t>
   </si>
@@ -127,6 +127,18 @@
   </si>
   <si>
     <t>王澔博</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Paz_Soldan_DIIID_NF_2024</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Paz_Soldan_DIIID_PPCF_2021</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pochelon_TCV_NF_1999</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
@@ -573,10 +585,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="1" max="1" width="41.83203125" customWidth="1"/>
     <col min="2" max="2" width="28.25" customWidth="1"/>
     <col min="3" max="3" width="28.08203125" customWidth="1"/>
     <col min="4" max="4" width="22.33203125" customWidth="1"/>
@@ -617,7 +629,7 @@
       </c>
       <c r="J2" s="6">
         <f>COUNTA(A5:A200)</f>
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="9.75" customHeight="1">
@@ -635,7 +647,7 @@
       </c>
       <c r="J3" s="7">
         <f>COUNTIF(B5:B200,"是")</f>
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="32.5" customHeight="1">
@@ -665,7 +677,7 @@
       </c>
       <c r="J4" s="7">
         <f>COUNTIF(C5:C200,"是")</f>
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="32.5" customHeight="1">
@@ -704,7 +716,7 @@
         <v>17</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="D6" s="16" t="s">
         <v>17</v>
@@ -724,7 +736,7 @@
         <v>16</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="D7" s="16" t="s">
         <v>17</v>
@@ -764,7 +776,7 @@
         <v>16</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="D9" s="16" t="s">
         <v>17</v>
@@ -784,7 +796,7 @@
         <v>17</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="D10" s="16" t="s">
         <v>17</v>
@@ -796,7 +808,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="16.5">
+    <row r="11" spans="1:10" ht="32.5" customHeight="1">
       <c r="A11" s="16" t="s">
         <v>25</v>
       </c>
@@ -813,6 +825,66 @@
         <v>28</v>
       </c>
       <c r="F11" s="16" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="32.5" customHeight="1">
+      <c r="A12" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="E12" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="F12" s="16" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="32.5" customHeight="1">
+      <c r="A13" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="D13" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="E13" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="F13" s="16" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="32.5" customHeight="1">
+      <c r="A14" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="D14" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="E14" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="F14" s="16" t="s">
         <v>29</v>
       </c>
     </row>

--- a/论文处理信息登记表.xlsx
+++ b/论文处理信息登记表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\Date Record\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6BD4EBF-D572-4B0C-A190-7CEE99CC7E30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8478CD53-22B1-49AB-81C2-EF291CE66462}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="556" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Paper Registry" sheetId="1" r:id="rId1"/>
@@ -119,12 +119,6 @@
     <t>Merlo_TCV_PoP_2019</t>
   </si>
   <si>
-    <t>Paz_Soldan_DIIID_NF_2024</t>
-  </si>
-  <si>
-    <t>Paz_Soldan_DIIID_PPCF_2021</t>
-  </si>
-  <si>
     <t>Pochelon_TCV_NF_1999</t>
   </si>
   <si>
@@ -133,6 +127,14 @@
   </si>
   <si>
     <t>否</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Paz-Soldan_DIIID_PPCF_2021</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Paz-Soldan_DIIID_NF_2024</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -590,7 +592,7 @@
         <v>21</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>17</v>
@@ -621,7 +623,7 @@
         <v>23</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>16</v>
@@ -645,7 +647,7 @@
         <v>24</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>16</v>
@@ -669,7 +671,7 @@
         <v>25</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>16</v>
@@ -693,7 +695,7 @@
         <v>26</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>17</v>
@@ -717,7 +719,7 @@
         <v>27</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>16</v>
@@ -738,10 +740,10 @@
     </row>
     <row r="12" spans="1:11" ht="32.5" customHeight="1">
       <c r="A12" s="5" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>17</v>
@@ -762,10 +764,10 @@
     </row>
     <row r="13" spans="1:11" ht="32.5" customHeight="1">
       <c r="A13" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>17</v>
@@ -786,10 +788,10 @@
     </row>
     <row r="14" spans="1:11" ht="32.5" customHeight="1">
       <c r="A14" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="6" t="s">
         <v>30</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>32</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>16</v>

--- a/论文处理信息登记表.xlsx
+++ b/论文处理信息登记表.xlsx
@@ -1,39 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\Date Record\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\37857\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8478CD53-22B1-49AB-81C2-EF291CE66462}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A01083A-5012-4672-8A7E-918579752422}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="556" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Paper Registry" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="40">
   <si>
     <t>Paper 数据登记表</t>
   </si>
@@ -41,7 +33,7 @@
     <t>统计</t>
   </si>
   <si>
-    <t>用于逐篇记录 NT实验/NT模拟/PT情况与复审状态</t>
+    <t>用于逐篇记录 paperid、模拟/PT情况与复审状态</t>
   </si>
   <si>
     <t>已登记论文数</t>
@@ -50,16 +42,13 @@
     <t>布尔字段统一使用“是 / 否”；QA 建议填写“通过 / 待补充 / 待复审”</t>
   </si>
   <si>
-    <t>含 NT 模拟数据</t>
+    <t>含模拟数据</t>
   </si>
   <si>
     <t>paperid</t>
   </si>
   <si>
-    <t>是否含 NT 实验数据</t>
-  </si>
-  <si>
-    <t>是否含 NT 模拟数据</t>
+    <t>是否有模拟数据</t>
   </si>
   <si>
     <t>是否有 PT 数据</t>
@@ -80,6 +69,9 @@
     <t>含 PT 数据</t>
   </si>
   <si>
+    <t>已复审</t>
+  </si>
+  <si>
     <t>Aucone_AUG_PPCF_2024</t>
   </si>
   <si>
@@ -95,15 +87,9 @@
     <t>王澔博</t>
   </si>
   <si>
-    <t>含 NT 实验数据</t>
-  </si>
-  <si>
     <t>Moret_TCV_PRL_1997</t>
   </si>
   <si>
-    <t>已复审</t>
-  </si>
-  <si>
     <t>Merlo_TOKAMAK_PoP_2023</t>
   </si>
   <si>
@@ -117,32 +103,70 @@
   </si>
   <si>
     <t>Merlo_TCV_PoP_2019</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>是</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>否</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>待复审</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>王澔博</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Paz_Soldan_DIIID_NF_2024</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Paz_Soldan_DIIID_PPCF_2021</t>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Pochelon_TCV_NF_1999</t>
-  </si>
-  <si>
-    <t>是</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>否</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Paz-Soldan_DIIID_PPCF_2021</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Paz-Soldan_DIIID_NF_2024</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>徐逸川</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Balestri_SMART_PPCF_2024</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Balestri_MULTI_PPCF_2025</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Balestri_TCV_PPCF_2024</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Schwartz_DEMO_NF_2022</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sheffield_GENERIC_FST_2016</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sauter_DEMO_FED_2016</t>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -154,6 +178,24 @@
       <name val="Carlito"/>
     </font>
     <font>
+      <b/>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FF334155"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF475569"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color rgb="FF1F2937"/>
       <name val="Carlito"/>
@@ -178,6 +220,12 @@
       <sz val="9"/>
       <name val="宋体"/>
       <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
@@ -195,13 +243,8 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF1F2937"/>
-      <name val="Carlito"/>
-    </font>
   </fonts>
-  <fills count="8">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -215,12 +258,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFECF1F7"/>
+        <fgColor rgb="FFD7DEE8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7F9FC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF4E6A8D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBFDFF"/>
       </patternFill>
     </fill>
     <fill>
@@ -238,8 +291,76 @@
         <fgColor rgb="FFE5F2E8"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFECF1F7"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="10">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -250,41 +371,71 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -454,379 +605,446 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="29.75" customWidth="1"/>
-    <col min="2" max="2" width="32.33203125" customWidth="1"/>
-    <col min="3" max="3" width="30.5" customWidth="1"/>
-    <col min="4" max="4" width="28.08203125" customWidth="1"/>
-    <col min="5" max="5" width="22.33203125" customWidth="1"/>
-    <col min="6" max="7" width="20.58203125" customWidth="1"/>
-    <col min="8" max="8" width="12" customWidth="1"/>
-    <col min="9" max="9" width="4" customWidth="1"/>
-    <col min="10" max="10" width="16" customWidth="1"/>
-    <col min="11" max="11" width="10" customWidth="1"/>
+    <col min="1" max="1" width="41.83203125" customWidth="1"/>
+    <col min="2" max="2" width="28.25" customWidth="1"/>
+    <col min="3" max="3" width="28.08203125" customWidth="1"/>
+    <col min="4" max="4" width="22.33203125" customWidth="1"/>
+    <col min="5" max="6" width="20.58203125" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="8" max="8" width="4" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="10" max="10" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="17.399999999999999" customHeight="1">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:10" ht="10.65" customHeight="1">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="J1" s="11" t="s">
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="I1" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="K1" s="11"/>
-    </row>
-    <row r="2" spans="1:11" ht="14.65" customHeight="1">
-      <c r="A2" s="10" t="s">
+      <c r="J1" s="21"/>
+    </row>
+    <row r="2" spans="1:10" ht="9.75" customHeight="1">
+      <c r="A2" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="J2" s="3" t="s">
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="I2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K2" s="3">
-        <f>COUNTA(A5:A1000)</f>
+      <c r="J2" s="6">
+        <f>COUNTA(A5:A200)</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="9.75" customHeight="1">
+      <c r="A3" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="19"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="19"/>
+      <c r="I3" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="J3" s="7">
+        <f>COUNTIF(B5:B200,"是")</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="32.5" customHeight="1">
+      <c r="A4" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="10" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" ht="14.65" customHeight="1">
-      <c r="A3" s="10" t="s">
+      <c r="F4" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="J4" s="7">
+        <f>COUNTIF(C5:C200,"是")</f>
         <v>4</v>
       </c>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10"/>
-      <c r="J3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K3" s="3">
-        <f>COUNTIF(C5:C1000,"是")</f>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="32.5" customHeight="1">
-      <c r="A4" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="J4" s="3" t="s">
+    </row>
+    <row r="5" spans="1:10" ht="32.5" customHeight="1">
+      <c r="A5" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="G5" s="2"/>
+      <c r="I5" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="K4" s="3">
-        <f>COUNTIF(D5:D1000,"是")</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="32.5" customHeight="1">
-      <c r="A5" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" s="6" t="s">
+      <c r="J5" s="8">
+        <f>COUNTIF(D5:D200,"是")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="32.5" customHeight="1">
+      <c r="A6" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" s="16" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="32.5" customHeight="1">
+      <c r="A7" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C7" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="32.5" customHeight="1">
+      <c r="A8" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="C8" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="D8" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="E8" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="F8" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="H5" s="2"/>
-      <c r="J5" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K5" s="3">
-        <f>COUNTIF(B5:B1000,"是")</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="32.5" customHeight="1">
-      <c r="A6" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" s="6" t="s">
+    </row>
+    <row r="9" spans="1:10" ht="32.5" customHeight="1">
+      <c r="A9" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="F9" s="16" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="32.5" customHeight="1">
+      <c r="A10" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="E10" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" s="16" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="32.5" customHeight="1">
+      <c r="A11" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="E11" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="F11" s="16" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="32.5" customHeight="1">
+      <c r="A12" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="C6" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="H6" s="2"/>
-      <c r="J6" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="K6" s="3">
-        <f>COUNTIF(E5:E1000,"是")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="32.5" customHeight="1">
-      <c r="A7" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="H7" s="2"/>
-    </row>
-    <row r="8" spans="1:11" ht="32.5" customHeight="1">
-      <c r="A8" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8" s="6" t="s">
+      <c r="B12" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="E12" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="F12" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="H8" s="2"/>
-    </row>
-    <row r="9" spans="1:11" ht="32.5" customHeight="1">
-      <c r="A9" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="H9" s="2"/>
-    </row>
-    <row r="10" spans="1:11" ht="32.5" customHeight="1">
-      <c r="A10" s="5" t="s">
+    </row>
+    <row r="13" spans="1:10" ht="32.5" customHeight="1">
+      <c r="A13" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="D13" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="E13" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="F13" s="16" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="32.5" customHeight="1">
+      <c r="A14" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="C14" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="D14" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="E14" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="F14" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="H10" s="2"/>
-    </row>
-    <row r="11" spans="1:11" ht="32.5" customHeight="1">
-      <c r="A11" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="H11" s="2"/>
-    </row>
-    <row r="12" spans="1:11" ht="32.5" customHeight="1">
-      <c r="A12" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="H12" s="2"/>
-    </row>
-    <row r="13" spans="1:11" ht="32.5" customHeight="1">
-      <c r="A13" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="H13" s="2"/>
-    </row>
-    <row r="14" spans="1:11" ht="32.5" customHeight="1">
-      <c r="A14" s="5" t="s">
+    </row>
+    <row r="15" spans="1:10" ht="33" customHeight="1">
+      <c r="A15" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B15" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="D15" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="E15" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="H14" s="2"/>
+      <c r="F15" s="16" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="32.5" customHeight="1">
+      <c r="A16" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="D16" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="E16" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="F16" s="16" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="32.5" customHeight="1">
+      <c r="A17" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="B17" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="C17" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="D17" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="E17" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="F17" s="16" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="33" customHeight="1">
+      <c r="A18" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="D18" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="E18" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="F18" s="16" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="32.5" customHeight="1">
+      <c r="A19" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="D19" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="E19" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="F19" s="16" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="33" customHeight="1">
+      <c r="A20" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="D20" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="E20" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="F20" s="16" t="s">
+        <v>33</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="I1:J1"/>
   </mergeCells>
-  <phoneticPr fontId="6" type="noConversion"/>
-  <dataValidations count="3">
+  <phoneticPr fontId="9" type="noConversion"/>
+  <dataValidations count="2">
     <dataValidation type="list" sqref="B5:D5" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"是,否"</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="E5" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"通过,待补充,待复审"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" sqref="B5:F100" xr:uid="{00000000-0002-0000-0000-000002000000}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/论文处理信息登记表.xlsx
+++ b/论文处理信息登记表.xlsx
@@ -1,31 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\37857\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\Date Record\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A01083A-5012-4672-8A7E-918579752422}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92B02993-E14A-412F-8930-90325BF8D526}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Paper Registry" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="43">
   <si>
     <t>Paper 数据登记表</t>
   </si>
@@ -159,6 +167,18 @@
   </si>
   <si>
     <t>Sauter_DEMO_FED_2016</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rewoldt_ISXB_PhysFluids_1982</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Riva_TOKAMAK_PPCF_2017</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wang_TOK_NF_2023</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
@@ -605,7 +625,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="41.83203125" customWidth="1"/>
@@ -649,7 +669,7 @@
       </c>
       <c r="J2" s="6">
         <f>COUNTA(A5:A200)</f>
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="9.75" customHeight="1">
@@ -1026,6 +1046,66 @@
       </c>
       <c r="F20" s="16" t="s">
         <v>33</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="16.5">
+      <c r="A21" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="D21" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="E21" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="F21" s="16" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="16.5">
+      <c r="A22" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="B22" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="D22" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="E22" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="F22" s="16" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="16.5">
+      <c r="A23" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="B23" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="C23" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="D23" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="E23" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="F23" s="16" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/论文处理信息登记表.xlsx
+++ b/论文处理信息登记表.xlsx
@@ -1,39 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\Date Record\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\37857\Desktop\git库\date-record-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92B02993-E14A-412F-8930-90325BF8D526}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CFD37B8-A5AF-45CE-94EC-692B3F01188E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Paper Registry" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="47">
   <si>
     <t>Paper 数据登记表</t>
   </si>
@@ -179,6 +171,22 @@
   </si>
   <si>
     <t>Wang_TOK_NF_2023</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Slendebroek_DIIID_NF_2026</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Coda_TCV_PPCF_2022</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Coda_TCV_NF_2019</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Happel_AUG_NF_2023</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
@@ -625,7 +633,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:J27"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="41.83203125" customWidth="1"/>
@@ -669,7 +677,7 @@
       </c>
       <c r="J2" s="6">
         <f>COUNTA(A5:A200)</f>
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="9.75" customHeight="1">
@@ -687,7 +695,7 @@
       </c>
       <c r="J3" s="7">
         <f>COUNTIF(B5:B200,"是")</f>
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="32.5" customHeight="1">
@@ -717,7 +725,7 @@
       </c>
       <c r="J4" s="7">
         <f>COUNTIF(C5:C200,"是")</f>
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="32.5" customHeight="1">
@@ -1106,6 +1114,86 @@
       </c>
       <c r="F23" s="16" t="s">
         <v>29</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="16.5">
+      <c r="A24" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="B24" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="D24" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="E24" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="F24" s="16" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="16.5">
+      <c r="A25" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="B25" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="C25" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="D25" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="E25" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="F25" s="16" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="16.5">
+      <c r="A26" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="B26" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="C26" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="D26" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="E26" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="F26" s="16" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="16.5">
+      <c r="A27" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="B27" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="C27" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="D27" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="E27" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="F27" s="16" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/论文处理信息登记表.xlsx
+++ b/论文处理信息登记表.xlsx
@@ -1,39 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\Date Record\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\37857\Desktop\git库\date-record-main\date-record\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8478CD53-22B1-49AB-81C2-EF291CE66462}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FACF532D-D585-460C-9E24-4CE1A50E5587}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="556" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="556" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Paper Registry" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="44">
   <si>
     <t>Paper 数据登记表</t>
   </si>
@@ -135,6 +127,40 @@
   </si>
   <si>
     <t>Paz-Soldan_DIIID_NF_2024</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Balestri_SMART_PPCF_2024</t>
+  </si>
+  <si>
+    <t>Balestri_MULTI_PPCF_2025</t>
+  </si>
+  <si>
+    <t>Balestri_TCV_PPCF_2024</t>
+  </si>
+  <si>
+    <t>Sauter_DEMO_FED_2016</t>
+  </si>
+  <si>
+    <t>Schwartz_DEMO_NF_2022</t>
+  </si>
+  <si>
+    <t>Sheffield_GENERIC_FST_2016</t>
+  </si>
+  <si>
+    <t>Slendebroek_DIIID_NF_2026</t>
+  </si>
+  <si>
+    <t>Coda_TCV_PPCF_2022</t>
+  </si>
+  <si>
+    <t>Coda_TCV_NF_2019</t>
+  </si>
+  <si>
+    <t>Happel_AUG_NF_2023</t>
+  </si>
+  <si>
+    <t>徐逸川</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -252,7 +278,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -287,6 +313,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -454,7 +481,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="29.75" customWidth="1"/>
@@ -500,8 +527,8 @@
         <v>3</v>
       </c>
       <c r="K2" s="3">
-        <f>COUNTA(A5:A1000)</f>
-        <v>10</v>
+        <f>COUNTA(A5:A976)</f>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="14.65" customHeight="1">
@@ -519,7 +546,7 @@
         <v>5</v>
       </c>
       <c r="K3" s="3">
-        <f>COUNTIF(C5:C1000,"是")</f>
+        <f>COUNTIF(C5:C976,"是")</f>
         <v>6</v>
       </c>
     </row>
@@ -552,8 +579,8 @@
         <v>14</v>
       </c>
       <c r="K4" s="3">
-        <f>COUNTIF(D5:D1000,"是")</f>
-        <v>3</v>
+        <f>COUNTIF(D5:D976,"是")</f>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="32.5" customHeight="1">
@@ -583,8 +610,8 @@
         <v>20</v>
       </c>
       <c r="K5" s="3">
-        <f>COUNTIF(B5:B1000,"是")</f>
-        <v>4</v>
+        <f>COUNTIF(B5:B976,"是")</f>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="32.5" customHeight="1">
@@ -614,7 +641,7 @@
         <v>22</v>
       </c>
       <c r="K6" s="3">
-        <f>COUNTIF(E5:E1000,"是")</f>
+        <f>COUNTIF(E5:E976,"是")</f>
         <v>0</v>
       </c>
     </row>
@@ -809,6 +836,270 @@
         <v>19</v>
       </c>
       <c r="H14" s="2"/>
+    </row>
+    <row r="15" spans="1:11" s="12" customFormat="1" ht="32.5" customHeight="1">
+      <c r="A15" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="H15" s="2"/>
+    </row>
+    <row r="16" spans="1:11" s="12" customFormat="1" ht="32.5" customHeight="1">
+      <c r="A16" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="H16" s="2"/>
+    </row>
+    <row r="17" spans="1:8" s="12" customFormat="1" ht="32.5" customHeight="1">
+      <c r="A17" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="H17" s="2"/>
+    </row>
+    <row r="18" spans="1:8" s="12" customFormat="1" ht="32.5" customHeight="1">
+      <c r="A18" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="H18" s="2"/>
+    </row>
+    <row r="19" spans="1:8" s="12" customFormat="1" ht="32.5" customHeight="1">
+      <c r="A19" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="H19" s="2"/>
+    </row>
+    <row r="20" spans="1:8" s="12" customFormat="1" ht="32.5" customHeight="1">
+      <c r="A20" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="H20" s="2"/>
+    </row>
+    <row r="21" spans="1:8" s="12" customFormat="1" ht="32.5" customHeight="1">
+      <c r="A21" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="H21" s="2"/>
+    </row>
+    <row r="22" spans="1:8" s="12" customFormat="1" ht="32.5" customHeight="1">
+      <c r="A22" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="H22" s="2"/>
+    </row>
+    <row r="23" spans="1:8" s="12" customFormat="1" ht="32.5" customHeight="1">
+      <c r="A23" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="H23" s="2"/>
+    </row>
+    <row r="24" spans="1:8" s="12" customFormat="1" ht="32.5" customHeight="1">
+      <c r="A24" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="H24" s="2"/>
+    </row>
+    <row r="25" spans="1:8" s="12" customFormat="1" ht="32.5" customHeight="1">
+      <c r="A25" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="H25" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -825,8 +1116,9 @@
     <dataValidation type="list" sqref="E5" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"通过,待补充,待复审"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" sqref="B5:F100" xr:uid="{00000000-0002-0000-0000-000002000000}"/>
+    <dataValidation allowBlank="1" sqref="B5:F76" xr:uid="{00000000-0002-0000-0000-000002000000}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/论文处理信息登记表.xlsx
+++ b/论文处理信息登记表.xlsx
@@ -1,31 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\37857\Desktop\git库\date-record-main\date-record\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\Date Record\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FACF532D-D585-460C-9E24-4CE1A50E5587}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEF55457-9821-4AEC-B00B-E102D774840A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="556" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="380" yWindow="380" windowWidth="17760" windowHeight="12700" tabRatio="556" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Paper Registry" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="48">
   <si>
     <t>Paper 数据登记表</t>
   </si>
@@ -161,6 +169,22 @@
   </si>
   <si>
     <t>徐逸川</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ren_ReactorTokamak_PPCF_2016</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>王澔博</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rewoldt_ISXB_PoF_1982</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Singh_TOK_NF_2023</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -278,7 +302,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -313,7 +337,6 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -481,7 +504,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="29.75" customWidth="1"/>
@@ -528,7 +551,7 @@
       </c>
       <c r="K2" s="3">
         <f>COUNTA(A5:A976)</f>
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="14.65" customHeight="1">
@@ -837,7 +860,7 @@
       </c>
       <c r="H14" s="2"/>
     </row>
-    <row r="15" spans="1:11" s="12" customFormat="1" ht="32.5" customHeight="1">
+    <row r="15" spans="1:11" ht="32.5" customHeight="1">
       <c r="A15" s="5" t="s">
         <v>28</v>
       </c>
@@ -861,7 +884,7 @@
       </c>
       <c r="H15" s="2"/>
     </row>
-    <row r="16" spans="1:11" s="12" customFormat="1" ht="32.5" customHeight="1">
+    <row r="16" spans="1:11" ht="32.5" customHeight="1">
       <c r="A16" s="5" t="s">
         <v>33</v>
       </c>
@@ -885,7 +908,7 @@
       </c>
       <c r="H16" s="2"/>
     </row>
-    <row r="17" spans="1:8" s="12" customFormat="1" ht="32.5" customHeight="1">
+    <row r="17" spans="1:8" ht="32.5" customHeight="1">
       <c r="A17" s="5" t="s">
         <v>34</v>
       </c>
@@ -909,7 +932,7 @@
       </c>
       <c r="H17" s="2"/>
     </row>
-    <row r="18" spans="1:8" s="12" customFormat="1" ht="32.5" customHeight="1">
+    <row r="18" spans="1:8" ht="32.5" customHeight="1">
       <c r="A18" s="5" t="s">
         <v>35</v>
       </c>
@@ -933,7 +956,7 @@
       </c>
       <c r="H18" s="2"/>
     </row>
-    <row r="19" spans="1:8" s="12" customFormat="1" ht="32.5" customHeight="1">
+    <row r="19" spans="1:8" ht="32.5" customHeight="1">
       <c r="A19" s="5" t="s">
         <v>36</v>
       </c>
@@ -957,7 +980,7 @@
       </c>
       <c r="H19" s="2"/>
     </row>
-    <row r="20" spans="1:8" s="12" customFormat="1" ht="32.5" customHeight="1">
+    <row r="20" spans="1:8" ht="32.5" customHeight="1">
       <c r="A20" s="5" t="s">
         <v>37</v>
       </c>
@@ -981,7 +1004,7 @@
       </c>
       <c r="H20" s="2"/>
     </row>
-    <row r="21" spans="1:8" s="12" customFormat="1" ht="32.5" customHeight="1">
+    <row r="21" spans="1:8" ht="32.5" customHeight="1">
       <c r="A21" s="5" t="s">
         <v>38</v>
       </c>
@@ -1005,7 +1028,7 @@
       </c>
       <c r="H21" s="2"/>
     </row>
-    <row r="22" spans="1:8" s="12" customFormat="1" ht="32.5" customHeight="1">
+    <row r="22" spans="1:8" ht="32.5" customHeight="1">
       <c r="A22" s="5" t="s">
         <v>39</v>
       </c>
@@ -1029,7 +1052,7 @@
       </c>
       <c r="H22" s="2"/>
     </row>
-    <row r="23" spans="1:8" s="12" customFormat="1" ht="32.5" customHeight="1">
+    <row r="23" spans="1:8" ht="32.5" customHeight="1">
       <c r="A23" s="5" t="s">
         <v>40</v>
       </c>
@@ -1053,7 +1076,7 @@
       </c>
       <c r="H23" s="2"/>
     </row>
-    <row r="24" spans="1:8" s="12" customFormat="1" ht="32.5" customHeight="1">
+    <row r="24" spans="1:8" ht="32.5" customHeight="1">
       <c r="A24" s="5" t="s">
         <v>41</v>
       </c>
@@ -1077,7 +1100,7 @@
       </c>
       <c r="H24" s="2"/>
     </row>
-    <row r="25" spans="1:8" s="12" customFormat="1" ht="32.5" customHeight="1">
+    <row r="25" spans="1:8" ht="32.5" customHeight="1">
       <c r="A25" s="5" t="s">
         <v>42</v>
       </c>
@@ -1100,6 +1123,77 @@
         <v>43</v>
       </c>
       <c r="H25" s="2"/>
+    </row>
+    <row r="26" spans="1:8" ht="33">
+      <c r="A26" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="H26" s="2"/>
+    </row>
+    <row r="27" spans="1:8" ht="16.5">
+      <c r="A27" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="H27" s="2"/>
+    </row>
+    <row r="28" spans="1:8" ht="16.5">
+      <c r="A28" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G28" s="5" t="s">
+        <v>45</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="4">

--- a/论文处理信息登记表.xlsx
+++ b/论文处理信息登记表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\Date Record\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEF55457-9821-4AEC-B00B-E102D774840A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C79F249-391B-4BC6-BE25-14BACE9C4083}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="380" windowWidth="17760" windowHeight="12700" tabRatio="556" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="556" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Paper Registry" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="49">
   <si>
     <t>Paper 数据登记表</t>
   </si>
@@ -185,6 +185,10 @@
   </si>
   <si>
     <t>Singh_TOK_NF_2023</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rienacker_TCV_NF_2026</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -504,7 +508,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K28"/>
+  <dimension ref="A1:K29"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="29.75" customWidth="1"/>
@@ -551,7 +555,7 @@
       </c>
       <c r="K2" s="3">
         <f>COUNTA(A5:A976)</f>
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="14.65" customHeight="1">
@@ -603,7 +607,7 @@
       </c>
       <c r="K4" s="3">
         <f>COUNTIF(D5:D976,"是")</f>
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="32.5" customHeight="1">
@@ -634,7 +638,7 @@
       </c>
       <c r="K5" s="3">
         <f>COUNTIF(B5:B976,"是")</f>
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="32.5" customHeight="1">
@@ -1194,6 +1198,31 @@
       <c r="G28" s="5" t="s">
         <v>45</v>
       </c>
+      <c r="H28" s="2"/>
+    </row>
+    <row r="29" spans="1:8" ht="16.5">
+      <c r="A29" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F29" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="H29" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="4">

--- a/论文处理信息登记表.xlsx
+++ b/论文处理信息登记表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\Date Record\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C79F249-391B-4BC6-BE25-14BACE9C4083}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49D803D0-CF13-4F16-9037-6FAD1FFD64B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="556" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="52">
   <si>
     <t>Paper 数据登记表</t>
   </si>
@@ -189,6 +189,18 @@
   </si>
   <si>
     <t>Rienacker_TCV_NF_2026</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Scotti_DIII-D_NF_2024</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Saarelma_DIII-D_PPCF_2021</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sciortino_DIIID_PPCF_2022</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -508,7 +520,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K29"/>
+  <dimension ref="A1:K32"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="29.75" customWidth="1"/>
@@ -555,7 +567,7 @@
       </c>
       <c r="K2" s="3">
         <f>COUNTA(A5:A976)</f>
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="14.65" customHeight="1">
@@ -574,7 +586,7 @@
       </c>
       <c r="K3" s="3">
         <f>COUNTIF(C5:C976,"是")</f>
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="32.5" customHeight="1">
@@ -607,7 +619,7 @@
       </c>
       <c r="K4" s="3">
         <f>COUNTIF(D5:D976,"是")</f>
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="32.5" customHeight="1">
@@ -638,7 +650,7 @@
       </c>
       <c r="K5" s="3">
         <f>COUNTIF(B5:B976,"是")</f>
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="32.5" customHeight="1">
@@ -1223,6 +1235,75 @@
         <v>45</v>
       </c>
       <c r="H29" s="2"/>
+    </row>
+    <row r="30" spans="1:8" ht="16.5">
+      <c r="A30" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F30" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G30" s="5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="16.5">
+      <c r="A31" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F31" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G31" s="5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="16.5">
+      <c r="A32" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="F32" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G32" s="5" t="s">
+        <v>45</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="4">

--- a/论文处理信息登记表.xlsx
+++ b/论文处理信息登记表.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\Date Record\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rockie\Desktop\大创\Date Record\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2104709E-AAE8-49D3-BB2B-4FE5845774AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FE730BE-6EB7-4F8E-AFEB-9F827A848755}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="451" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,8 +24,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -33,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="56">
   <si>
     <t>Paper 数据登记表</t>
   </si>
@@ -199,6 +197,14 @@
   </si>
   <si>
     <t>Zhou_EUDEMO_PPCF_2021</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fevrier_TCV_PPCF_2024</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>刘芸琪</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -338,15 +344,6 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -360,6 +357,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -529,7 +535,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K35"/>
+  <dimension ref="A1:K36"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="42.453125" customWidth="1"/>
@@ -545,79 +551,77 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="17.399999999999999" customHeight="1">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="J1" s="5" t="s">
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="J1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="K1" s="5"/>
+      <c r="K1" s="10"/>
     </row>
     <row r="2" spans="1:11" ht="14.65" customHeight="1">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="11"/>
+      <c r="H2" s="11"/>
       <c r="J2" s="1" t="s">
         <v>3</v>
       </c>
       <c r="K2" s="1">
-        <f>COUNTA(A5:A976)</f>
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="14.65" customHeight="1">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11"/>
       <c r="J3" s="1" t="s">
         <v>5</v>
       </c>
       <c r="K3" s="1">
-        <f>COUNTIF(C5:C976,"是")</f>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="25.5" customHeight="1">
+      <c r="A4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" ht="25.5" customHeight="1">
-      <c r="A4" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4" s="7" t="s">
+      <c r="G4" s="4" t="s">
         <v>12</v>
       </c>
       <c r="H4" s="2" t="s">
@@ -627,30 +631,29 @@
         <v>14</v>
       </c>
       <c r="K4" s="1">
-        <f>COUNTIF(D5:D976,"是")</f>
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="25.5" customHeight="1">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="F5" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="G5" s="8" t="s">
+      <c r="B5" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5" s="5" t="s">
         <v>19</v>
       </c>
       <c r="H5" s="3"/>
@@ -658,30 +661,29 @@
         <v>20</v>
       </c>
       <c r="K5" s="1">
-        <f>COUNTIF(B5:B976,"是")</f>
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="25.5" customHeight="1">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E6" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="F6" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="G6" s="8" t="s">
+      <c r="B6" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" s="5" t="s">
         <v>19</v>
       </c>
       <c r="H6" s="3"/>
@@ -694,700 +696,724 @@
       </c>
     </row>
     <row r="7" spans="1:11" ht="25.5" customHeight="1">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B7" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="F7" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="G7" s="8" t="s">
+      <c r="B7" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G7" s="5" t="s">
         <v>19</v>
       </c>
       <c r="H7" s="3"/>
     </row>
     <row r="8" spans="1:11" ht="25.5" customHeight="1">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E8" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="F8" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="G8" s="8" t="s">
+      <c r="B8" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G8" s="5" t="s">
         <v>19</v>
       </c>
       <c r="H8" s="3"/>
     </row>
     <row r="9" spans="1:11" ht="25.5" customHeight="1">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="F9" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="G9" s="8" t="s">
+      <c r="B9" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G9" s="5" t="s">
         <v>19</v>
       </c>
       <c r="H9" s="3"/>
     </row>
     <row r="10" spans="1:11" ht="25.5" customHeight="1">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E10" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="F10" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="G10" s="8" t="s">
+      <c r="B10" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G10" s="5" t="s">
         <v>19</v>
       </c>
       <c r="H10" s="3"/>
     </row>
     <row r="11" spans="1:11" ht="25.5" customHeight="1">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B11" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E11" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="F11" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="G11" s="8" t="s">
+      <c r="B11" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G11" s="5" t="s">
         <v>19</v>
       </c>
       <c r="H11" s="3"/>
     </row>
     <row r="12" spans="1:11" ht="25.5" customHeight="1">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E12" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="F12" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="G12" s="8" t="s">
+      <c r="B12" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G12" s="5" t="s">
         <v>19</v>
       </c>
       <c r="H12" s="3"/>
     </row>
     <row r="13" spans="1:11" ht="25.5" customHeight="1">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E13" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="F13" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="G13" s="8" t="s">
+      <c r="B13" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G13" s="5" t="s">
         <v>19</v>
       </c>
       <c r="H13" s="3"/>
     </row>
     <row r="14" spans="1:11" ht="25.5" customHeight="1">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B14" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E14" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="F14" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="G14" s="8" t="s">
+      <c r="B14" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G14" s="5" t="s">
         <v>19</v>
       </c>
       <c r="H14" s="3"/>
     </row>
     <row r="15" spans="1:11" ht="25.5" customHeight="1">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B15" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E15" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="F15" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="G15" s="8" t="s">
+      <c r="B15" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G15" s="5" t="s">
         <v>31</v>
       </c>
       <c r="H15" s="3"/>
     </row>
     <row r="16" spans="1:11" ht="25.5" customHeight="1">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B16" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="D16" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E16" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="F16" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="G16" s="8" t="s">
+      <c r="B16" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G16" s="5" t="s">
         <v>31</v>
       </c>
       <c r="H16" s="3"/>
     </row>
     <row r="17" spans="1:8" ht="25.5" customHeight="1">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="B17" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E17" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="F17" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="G17" s="8" t="s">
+      <c r="B17" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G17" s="5" t="s">
         <v>31</v>
       </c>
       <c r="H17" s="3"/>
     </row>
     <row r="18" spans="1:8" ht="25.5" customHeight="1">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B18" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="D18" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E18" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="F18" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="G18" s="8" t="s">
+      <c r="B18" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G18" s="5" t="s">
         <v>31</v>
       </c>
       <c r="H18" s="3"/>
     </row>
     <row r="19" spans="1:8" ht="25.5" customHeight="1">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B19" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="D19" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E19" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="F19" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="G19" s="8" t="s">
+      <c r="B19" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G19" s="5" t="s">
         <v>31</v>
       </c>
       <c r="H19" s="3"/>
     </row>
     <row r="20" spans="1:8" ht="25.5" customHeight="1">
-      <c r="A20" s="8" t="s">
+      <c r="A20" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="B20" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E20" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="F20" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="G20" s="8" t="s">
+      <c r="B20" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G20" s="5" t="s">
         <v>31</v>
       </c>
       <c r="H20" s="3"/>
     </row>
     <row r="21" spans="1:8" ht="25.5" customHeight="1">
-      <c r="A21" s="8" t="s">
+      <c r="A21" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B21" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C21" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="D21" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E21" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="F21" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="G21" s="8" t="s">
+      <c r="B21" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G21" s="5" t="s">
         <v>31</v>
       </c>
       <c r="H21" s="3"/>
     </row>
     <row r="22" spans="1:8" ht="25.5" customHeight="1">
-      <c r="A22" s="8" t="s">
+      <c r="A22" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C22" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="D22" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E22" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="F22" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="G22" s="8" t="s">
+      <c r="B22" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G22" s="5" t="s">
         <v>31</v>
       </c>
       <c r="H22" s="3"/>
     </row>
     <row r="23" spans="1:8" ht="25.5" customHeight="1">
-      <c r="A23" s="8" t="s">
+      <c r="A23" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B23" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C23" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="D23" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E23" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="F23" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="G23" s="8" t="s">
+      <c r="B23" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G23" s="5" t="s">
         <v>31</v>
       </c>
       <c r="H23" s="3"/>
     </row>
     <row r="24" spans="1:8" ht="25.5" customHeight="1">
-      <c r="A24" s="8" t="s">
+      <c r="A24" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B24" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="D24" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E24" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="F24" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="G24" s="8" t="s">
+      <c r="B24" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G24" s="5" t="s">
         <v>31</v>
       </c>
       <c r="H24" s="3"/>
     </row>
     <row r="25" spans="1:8" ht="25.5" customHeight="1">
-      <c r="A25" s="8" t="s">
+      <c r="A25" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B25" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C25" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="D25" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E25" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="F25" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="G25" s="8" t="s">
+      <c r="B25" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G25" s="5" t="s">
         <v>31</v>
       </c>
       <c r="H25" s="3"/>
     </row>
     <row r="26" spans="1:8" ht="25.5" customHeight="1">
-      <c r="A26" s="8" t="s">
+      <c r="A26" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B26" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="D26" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E26" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="F26" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="G26" s="8" t="s">
+      <c r="B26" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G26" s="5" t="s">
         <v>19</v>
       </c>
       <c r="H26" s="3"/>
     </row>
     <row r="27" spans="1:8" ht="25.5" customHeight="1">
-      <c r="A27" s="8" t="s">
+      <c r="A27" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B27" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C27" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="D27" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E27" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="F27" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="G27" s="8" t="s">
+      <c r="B27" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G27" s="5" t="s">
         <v>19</v>
       </c>
       <c r="H27" s="3"/>
     </row>
     <row r="28" spans="1:8" ht="25.5" customHeight="1">
-      <c r="A28" s="8" t="s">
+      <c r="A28" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B28" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C28" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="D28" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E28" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="F28" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="G28" s="8" t="s">
+      <c r="B28" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G28" s="5" t="s">
         <v>19</v>
       </c>
       <c r="H28" s="3"/>
     </row>
     <row r="29" spans="1:8" ht="25.5" customHeight="1">
-      <c r="A29" s="8" t="s">
+      <c r="A29" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B29" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C29" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="D29" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E29" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="F29" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="G29" s="8" t="s">
+      <c r="B29" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F29" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G29" s="5" t="s">
         <v>19</v>
       </c>
       <c r="H29" s="3"/>
     </row>
     <row r="30" spans="1:8" ht="25.5" customHeight="1">
-      <c r="A30" s="8" t="s">
+      <c r="A30" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="B30" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C30" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="D30" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E30" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="F30" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="G30" s="8" t="s">
+      <c r="B30" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F30" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G30" s="5" t="s">
         <v>19</v>
       </c>
       <c r="H30" s="3"/>
     </row>
     <row r="31" spans="1:8" ht="25.5" customHeight="1">
-      <c r="A31" s="8" t="s">
+      <c r="A31" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B31" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C31" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="D31" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E31" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="F31" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="G31" s="8" t="s">
+      <c r="B31" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F31" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G31" s="5" t="s">
         <v>19</v>
       </c>
       <c r="H31" s="3"/>
     </row>
     <row r="32" spans="1:8" ht="25.5" customHeight="1">
-      <c r="A32" s="8" t="s">
+      <c r="A32" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="B32" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C32" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="D32" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E32" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="F32" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="G32" s="8" t="s">
+      <c r="B32" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F32" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G32" s="5" t="s">
         <v>19</v>
       </c>
       <c r="H32" s="3"/>
     </row>
     <row r="33" spans="1:8" ht="25.5" customHeight="1">
-      <c r="A33" s="8" t="s">
+      <c r="A33" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B33" s="9" t="s">
+      <c r="B33" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="C33" s="9" t="s">
+      <c r="C33" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="D33" s="9" t="s">
+      <c r="D33" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="E33" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="F33" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="G33" s="8" t="s">
+      <c r="E33" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F33" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G33" s="5" t="s">
         <v>19</v>
       </c>
       <c r="H33" s="3"/>
     </row>
     <row r="34" spans="1:8" ht="25.5" customHeight="1">
-      <c r="A34" s="8" t="s">
+      <c r="A34" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="B34" s="9" t="s">
+      <c r="B34" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="C34" s="9" t="s">
+      <c r="C34" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="D34" s="9" t="s">
+      <c r="D34" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="E34" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="F34" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="G34" s="8" t="s">
+      <c r="E34" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F34" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G34" s="5" t="s">
         <v>19</v>
       </c>
       <c r="H34" s="3"/>
     </row>
     <row r="35" spans="1:8" ht="25.5" customHeight="1">
-      <c r="A35" s="8" t="s">
+      <c r="A35" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="B35" s="9" t="s">
+      <c r="B35" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="C35" s="9" t="s">
+      <c r="C35" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="D35" s="9" t="s">
+      <c r="D35" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="E35" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="F35" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="G35" s="8" t="s">
+      <c r="E35" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F35" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G35" s="5" t="s">
         <v>19</v>
       </c>
       <c r="H35" s="3"/>
+    </row>
+    <row r="36" spans="1:8" ht="14.5">
+      <c r="A36" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F36" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G36" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="H36" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="4">

--- a/论文处理信息登记表.xlsx
+++ b/论文处理信息登记表.xlsx
@@ -1,37 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rockie\Desktop\大创\Date Record\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\37857\Desktop\git库\date-record-main\date-record\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FE730BE-6EB7-4F8E-AFEB-9F827A848755}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{796133E2-430D-4E24-9A5C-F704B2B49072}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="451" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="451" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Paper Registry" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="68">
   <si>
     <t>Paper 数据登记表</t>
   </si>
@@ -205,6 +199,54 @@
   </si>
   <si>
     <t>刘芸琪</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Marinoni_DIII-D_TCV_IAEA-FEC_2020</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Marinoni_MULTI_RMPP_2021</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>徐逸川</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Kikuchi_MULTI_Energies_2014</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Kikuchi_MULTI_EPS_2015</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Kikuchi_MULTI_NF_2019</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Kikuchi_MULTI_JPSConfProc_2014</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Merle_TCV_PPCF_2017</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Kikuchi_SWIP_CONF_2025</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Nelson_REACTOR_NF_2022</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Nelson_MAST-U_NF_2024</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Nelson_DIII-D_ITPAPEP_2025</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -535,7 +577,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K36"/>
+  <dimension ref="A1:K47"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="42.453125" customWidth="1"/>
@@ -691,7 +733,7 @@
         <v>22</v>
       </c>
       <c r="K6" s="1">
-        <f>COUNTIF(E5:E976,"是")</f>
+        <f>COUNTIF(E5:E975,"是")</f>
         <v>0</v>
       </c>
     </row>
@@ -1391,7 +1433,7 @@
       </c>
       <c r="H35" s="3"/>
     </row>
-    <row r="36" spans="1:8" ht="14.5">
+    <row r="36" spans="1:8" ht="25.5" customHeight="1">
       <c r="A36" s="5" t="s">
         <v>54</v>
       </c>
@@ -1414,6 +1456,270 @@
         <v>55</v>
       </c>
       <c r="H36" s="3"/>
+    </row>
+    <row r="37" spans="1:8" ht="25.5" customHeight="1">
+      <c r="A37" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F37" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G37" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="H37" s="3"/>
+    </row>
+    <row r="38" spans="1:8" ht="25.5" customHeight="1">
+      <c r="A38" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F38" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G38" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="H38" s="3"/>
+    </row>
+    <row r="39" spans="1:8" ht="25.5" customHeight="1">
+      <c r="A39" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F39" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G39" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="H39" s="3"/>
+    </row>
+    <row r="40" spans="1:8" ht="25.5" customHeight="1">
+      <c r="A40" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F40" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G40" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="H40" s="3"/>
+    </row>
+    <row r="41" spans="1:8" ht="25.5" customHeight="1">
+      <c r="A41" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F41" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G41" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="H41" s="3"/>
+    </row>
+    <row r="42" spans="1:8" ht="25.5" customHeight="1">
+      <c r="A42" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="E42" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F42" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G42" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="H42" s="3"/>
+    </row>
+    <row r="43" spans="1:8" ht="25.5" customHeight="1">
+      <c r="A43" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="F43" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G43" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="H43" s="3"/>
+    </row>
+    <row r="44" spans="1:8" ht="25.5" customHeight="1">
+      <c r="A44" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="E44" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="F44" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G44" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="H44" s="3"/>
+    </row>
+    <row r="45" spans="1:8" ht="25.5" customHeight="1">
+      <c r="A45" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D45" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="E45" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="F45" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G45" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="H45" s="3"/>
+    </row>
+    <row r="46" spans="1:8" ht="25.5" customHeight="1">
+      <c r="A46" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="E46" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="F46" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G46" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="H46" s="3"/>
+    </row>
+    <row r="47" spans="1:8" ht="25.5" customHeight="1">
+      <c r="A47" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="E47" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="F47" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G47" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="H47" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -1433,6 +1739,6 @@
     <dataValidation allowBlank="1" sqref="F5" xr:uid="{00000000-0002-0000-0000-000002000000}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/论文处理信息登记表.xlsx
+++ b/论文处理信息登记表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\37857\Desktop\git库\date-record-main\date-record\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{796133E2-430D-4E24-9A5C-F704B2B49072}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD85CB12-D428-414D-A72F-BB89BD0FB170}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="451" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="68">
   <si>
     <t>Paper 数据登记表</t>
   </si>
@@ -577,7 +577,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K47"/>
+  <dimension ref="A1:K46"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="42.453125" customWidth="1"/>
@@ -733,7 +733,7 @@
         <v>22</v>
       </c>
       <c r="K6" s="1">
-        <f>COUNTIF(E5:E975,"是")</f>
+        <f>COUNTIF(E5:E974,"是")</f>
         <v>0</v>
       </c>
     </row>
@@ -931,7 +931,7 @@
     </row>
     <row r="15" spans="1:11" ht="25.5" customHeight="1">
       <c r="A15" s="5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>17</v>
@@ -940,7 +940,7 @@
         <v>17</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>17</v>
@@ -955,7 +955,7 @@
     </row>
     <row r="16" spans="1:11" ht="25.5" customHeight="1">
       <c r="A16" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>17</v>
@@ -964,7 +964,7 @@
         <v>17</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>17</v>
@@ -979,16 +979,16 @@
     </row>
     <row r="17" spans="1:8" ht="25.5" customHeight="1">
       <c r="A17" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>17</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E17" s="7" t="s">
         <v>17</v>
@@ -1003,16 +1003,16 @@
     </row>
     <row r="18" spans="1:8" ht="25.5" customHeight="1">
       <c r="A18" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>17</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E18" s="7" t="s">
         <v>17</v>
@@ -1027,7 +1027,7 @@
     </row>
     <row r="19" spans="1:8" ht="25.5" customHeight="1">
       <c r="A19" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>17</v>
@@ -1051,7 +1051,7 @@
     </row>
     <row r="20" spans="1:8" ht="25.5" customHeight="1">
       <c r="A20" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>17</v>
@@ -1075,10 +1075,10 @@
     </row>
     <row r="21" spans="1:8" ht="25.5" customHeight="1">
       <c r="A21" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>17</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="22" spans="1:8" ht="25.5" customHeight="1">
       <c r="A22" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>17</v>
@@ -1123,7 +1123,7 @@
     </row>
     <row r="23" spans="1:8" ht="25.5" customHeight="1">
       <c r="A23" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>17</v>
@@ -1147,10 +1147,10 @@
     </row>
     <row r="24" spans="1:8" ht="25.5" customHeight="1">
       <c r="A24" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>17</v>
@@ -1171,10 +1171,10 @@
     </row>
     <row r="25" spans="1:8" ht="25.5" customHeight="1">
       <c r="A25" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>17</v>
@@ -1189,13 +1189,13 @@
         <v>18</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="H25" s="3"/>
     </row>
     <row r="26" spans="1:8" ht="25.5" customHeight="1">
       <c r="A26" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>17</v>
@@ -1219,7 +1219,7 @@
     </row>
     <row r="27" spans="1:8" ht="25.5" customHeight="1">
       <c r="A27" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>17</v>
@@ -1243,16 +1243,16 @@
     </row>
     <row r="28" spans="1:8" ht="25.5" customHeight="1">
       <c r="A28" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>17</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E28" s="7" t="s">
         <v>17</v>
@@ -1267,16 +1267,16 @@
     </row>
     <row r="29" spans="1:8" ht="25.5" customHeight="1">
       <c r="A29" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>16</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E29" s="7" t="s">
         <v>17</v>
@@ -1291,7 +1291,7 @@
     </row>
     <row r="30" spans="1:8" ht="25.5" customHeight="1">
       <c r="A30" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>16</v>
@@ -1315,7 +1315,7 @@
     </row>
     <row r="31" spans="1:8" ht="25.5" customHeight="1">
       <c r="A31" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>16</v>
@@ -1324,7 +1324,7 @@
         <v>16</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E31" s="7" t="s">
         <v>17</v>
@@ -1339,16 +1339,16 @@
     </row>
     <row r="32" spans="1:8" ht="25.5" customHeight="1">
       <c r="A32" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="E32" s="7" t="s">
         <v>17</v>
@@ -1363,16 +1363,16 @@
     </row>
     <row r="33" spans="1:8" ht="25.5" customHeight="1">
       <c r="A33" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>50</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E33" s="7" t="s">
         <v>17</v>
@@ -1387,7 +1387,7 @@
     </row>
     <row r="34" spans="1:8" ht="25.5" customHeight="1">
       <c r="A34" s="5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>50</v>
@@ -1411,10 +1411,10 @@
     </row>
     <row r="35" spans="1:8" ht="25.5" customHeight="1">
       <c r="A35" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>52</v>
@@ -1429,22 +1429,22 @@
         <v>18</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="H35" s="3"/>
     </row>
     <row r="36" spans="1:8" ht="25.5" customHeight="1">
       <c r="A36" s="5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E36" s="7" t="s">
         <v>17</v>
@@ -1453,22 +1453,22 @@
         <v>18</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H36" s="3"/>
     </row>
     <row r="37" spans="1:8" ht="25.5" customHeight="1">
       <c r="A37" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>50</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E37" s="7" t="s">
         <v>17</v>
@@ -1483,7 +1483,7 @@
     </row>
     <row r="38" spans="1:8" ht="25.5" customHeight="1">
       <c r="A38" s="5" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>50</v>
@@ -1507,7 +1507,7 @@
     </row>
     <row r="39" spans="1:8" ht="25.5" customHeight="1">
       <c r="A39" s="5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>50</v>
@@ -1516,7 +1516,7 @@
         <v>52</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E39" s="7" t="s">
         <v>17</v>
@@ -1531,7 +1531,7 @@
     </row>
     <row r="40" spans="1:8" ht="25.5" customHeight="1">
       <c r="A40" s="5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>50</v>
@@ -1540,7 +1540,7 @@
         <v>52</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E40" s="7" t="s">
         <v>17</v>
@@ -1555,7 +1555,7 @@
     </row>
     <row r="41" spans="1:8" ht="25.5" customHeight="1">
       <c r="A41" s="5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>50</v>
@@ -1579,10 +1579,10 @@
     </row>
     <row r="42" spans="1:8" ht="25.5" customHeight="1">
       <c r="A42" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>52</v>
@@ -1591,7 +1591,7 @@
         <v>52</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="F42" s="8" t="s">
         <v>18</v>
@@ -1603,13 +1603,13 @@
     </row>
     <row r="43" spans="1:8" ht="25.5" customHeight="1">
       <c r="A43" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D43" s="6" t="s">
         <v>52</v>
@@ -1627,13 +1627,13 @@
     </row>
     <row r="44" spans="1:8" ht="25.5" customHeight="1">
       <c r="A44" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B44" s="6" t="s">
         <v>50</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D44" s="6" t="s">
         <v>52</v>
@@ -1651,16 +1651,16 @@
     </row>
     <row r="45" spans="1:8" ht="25.5" customHeight="1">
       <c r="A45" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B45" s="6" t="s">
         <v>50</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E45" s="7" t="s">
         <v>50</v>
@@ -1675,16 +1675,16 @@
     </row>
     <row r="46" spans="1:8" ht="25.5" customHeight="1">
       <c r="A46" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E46" s="7" t="s">
         <v>50</v>
@@ -1696,30 +1696,6 @@
         <v>58</v>
       </c>
       <c r="H46" s="3"/>
-    </row>
-    <row r="47" spans="1:8" ht="25.5" customHeight="1">
-      <c r="A47" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="C47" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="D47" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="E47" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="F47" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="G47" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="H47" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="4">

--- a/论文处理信息登记表.xlsx
+++ b/论文处理信息登记表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rockie\Desktop\大创\Date Record\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FE730BE-6EB7-4F8E-AFEB-9F827A848755}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8CE1E5C-2A5F-4138-999F-413BEFFA33D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="451" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="58">
   <si>
     <t>Paper 数据登记表</t>
   </si>
@@ -205,6 +205,14 @@
   </si>
   <si>
     <t>刘芸琪</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>待复审</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>通过</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -648,15 +656,17 @@
         <v>16</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="H5" s="3"/>
+      <c r="H5" s="3" t="s">
+        <v>55</v>
+      </c>
       <c r="J5" s="1" t="s">
         <v>20</v>
       </c>
@@ -678,21 +688,22 @@
         <v>17</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="G6" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="H6" s="3"/>
+      <c r="H6" s="3" t="s">
+        <v>55</v>
+      </c>
       <c r="J6" s="1" t="s">
         <v>22</v>
       </c>
       <c r="K6" s="1">
-        <f>COUNTIF(E5:E976,"是")</f>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="25.5" customHeight="1">
@@ -973,7 +984,7 @@
         <v>16</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="F18" s="8" t="s">
         <v>18</v>
@@ -981,7 +992,9 @@
       <c r="G18" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="H18" s="3"/>
+      <c r="H18" s="3" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="19" spans="1:8" ht="25.5" customHeight="1">
       <c r="A19" s="5" t="s">

--- a/论文处理信息登记表.xlsx
+++ b/论文处理信息登记表.xlsx
@@ -1,31 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\37857\Desktop\git库\date-record-main\date-record\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rockie\Desktop\大创\Date Record\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD85CB12-D428-414D-A72F-BB89BD0FB170}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE0A9485-A755-4E51-9D87-80BED38B4988}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="451" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="451" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Paper Registry" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="69">
   <si>
     <t>Paper 数据登记表</t>
   </si>
@@ -247,6 +253,10 @@
   </si>
   <si>
     <t>Nelson_DIII-D_ITPAPEP_2025</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>已复审</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -690,15 +700,17 @@
         <v>16</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="H5" s="3"/>
+      <c r="H5" s="3" t="s">
+        <v>55</v>
+      </c>
       <c r="J5" s="1" t="s">
         <v>20</v>
       </c>
@@ -734,7 +746,7 @@
       </c>
       <c r="K6" s="1">
         <f>COUNTIF(E5:E974,"是")</f>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="25.5" customHeight="1">
@@ -823,15 +835,17 @@
         <v>17</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G10" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="H10" s="3"/>
+      <c r="H10" s="3" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="11" spans="1:11" ht="25.5" customHeight="1">
       <c r="A11" s="5" t="s">
@@ -991,15 +1005,17 @@
         <v>16</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G17" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="H17" s="3"/>
+      <c r="H17" s="3" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="18" spans="1:8" ht="25.5" customHeight="1">
       <c r="A18" s="5" t="s">

--- a/论文处理信息登记表.xlsx
+++ b/论文处理信息登记表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rockie\Desktop\大创\Date Record\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE0A9485-A755-4E51-9D87-80BED38B4988}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63611F78-5B2C-4EF1-B7F3-B4FBD72B3714}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="451" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="69">
   <si>
     <t>Paper 数据登记表</t>
   </si>
@@ -745,8 +745,7 @@
         <v>22</v>
       </c>
       <c r="K6" s="1">
-        <f>COUNTIF(E5:E974,"是")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="25.5" customHeight="1">
@@ -1175,15 +1174,17 @@
         <v>17</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="G24" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="H24" s="3"/>
+      <c r="H24" s="3" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="25" spans="1:8" ht="25.5" customHeight="1">
       <c r="A25" s="5" t="s">

--- a/论文处理信息登记表.xlsx
+++ b/论文处理信息登记表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rockie\Desktop\大创\Date Record\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63611F78-5B2C-4EF1-B7F3-B4FBD72B3714}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50799B7D-7F9F-45C4-A997-B96B11062BF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="451" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="69">
   <si>
     <t>Paper 数据登记表</t>
   </si>
@@ -745,7 +745,7 @@
         <v>22</v>
       </c>
       <c r="K6" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="25.5" customHeight="1">
@@ -1608,15 +1608,17 @@
         <v>52</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F42" s="8" t="s">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="G42" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="H42" s="3"/>
+      <c r="H42" s="3" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="43" spans="1:8" ht="25.5" customHeight="1">
       <c r="A43" s="5" t="s">

--- a/论文处理信息登记表.xlsx
+++ b/论文处理信息登记表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rockie\Desktop\大创\Date Record\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50799B7D-7F9F-45C4-A997-B96B11062BF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71043C8C-A1CD-4047-B066-389B24AEC9FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="451" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="69">
   <si>
     <t>Paper 数据登记表</t>
   </si>
@@ -745,7 +745,7 @@
         <v>22</v>
       </c>
       <c r="K6" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="25.5" customHeight="1">
@@ -860,15 +860,17 @@
         <v>16</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="G11" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="H11" s="3"/>
+      <c r="H11" s="3" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="12" spans="1:11" ht="25.5" customHeight="1">
       <c r="A12" s="5" t="s">

--- a/论文处理信息登记表.xlsx
+++ b/论文处理信息登记表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rockie\Desktop\大创\Date Record\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71043C8C-A1CD-4047-B066-389B24AEC9FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70E1A1F2-4FCA-455F-836C-6DB9DBAF919E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="451" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="69">
   <si>
     <t>Paper 数据登记表</t>
   </si>
@@ -745,7 +745,7 @@
         <v>22</v>
       </c>
       <c r="K6" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="25.5" customHeight="1">
@@ -786,15 +786,17 @@
         <v>16</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="G8" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="H8" s="3"/>
+      <c r="H8" s="3" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="9" spans="1:11" ht="25.5" customHeight="1">
       <c r="A9" s="5" t="s">

--- a/论文处理信息登记表.xlsx
+++ b/论文处理信息登记表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rockie\Desktop\大创\Date Record\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70E1A1F2-4FCA-455F-836C-6DB9DBAF919E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7168E8B7-C570-4E12-9F95-73BEBCCD5F5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="451" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="69">
   <si>
     <t>Paper 数据登记表</t>
   </si>
@@ -745,7 +745,7 @@
         <v>22</v>
       </c>
       <c r="K6" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="25.5" customHeight="1">
@@ -1276,15 +1276,17 @@
         <v>16</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="G28" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="H28" s="3"/>
+      <c r="H28" s="3" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="29" spans="1:8" ht="25.5" customHeight="1">
       <c r="A29" s="5" t="s">

--- a/论文处理信息登记表.xlsx
+++ b/论文处理信息登记表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rockie\Desktop\大创\Date Record\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7168E8B7-C570-4E12-9F95-73BEBCCD5F5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{717B625D-9EF9-4C31-8D55-BB4016BF5EE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="451" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="69">
   <si>
     <t>Paper 数据登记表</t>
   </si>
@@ -745,7 +745,8 @@
         <v>22</v>
       </c>
       <c r="K6" s="1">
-        <v>8</v>
+        <f>--9</f>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="25.5" customHeight="1">
@@ -1350,15 +1351,17 @@
         <v>16</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="G31" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="H31" s="3"/>
+      <c r="H31" s="3" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="32" spans="1:8" ht="25.5" customHeight="1">
       <c r="A32" s="5" t="s">

--- a/论文处理信息登记表.xlsx
+++ b/论文处理信息登记表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rockie\Desktop\大创\Date Record\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{717B625D-9EF9-4C31-8D55-BB4016BF5EE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68A27BCD-3672-4CA1-888C-210A41023703}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="451" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="69">
   <si>
     <t>Paper 数据登记表</t>
   </si>
@@ -745,8 +745,7 @@
         <v>22</v>
       </c>
       <c r="K6" s="1">
-        <f>--9</f>
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="25.5" customHeight="1">
@@ -1327,15 +1326,17 @@
         <v>17</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="G30" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="H30" s="3"/>
+      <c r="H30" s="3" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="31" spans="1:8" ht="25.5" customHeight="1">
       <c r="A31" s="5" t="s">

--- a/论文处理信息登记表.xlsx
+++ b/论文处理信息登记表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rockie\Desktop\大创\Date Record\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68A27BCD-3672-4CA1-888C-210A41023703}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A339671C-CC75-430A-91F0-44874E77AA60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="451" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="69">
   <si>
     <t>Paper 数据登记表</t>
   </si>
@@ -715,7 +715,7 @@
         <v>20</v>
       </c>
       <c r="K5" s="1">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="25.5" customHeight="1">
@@ -745,7 +745,7 @@
         <v>22</v>
       </c>
       <c r="K6" s="1">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="25.5" customHeight="1">
@@ -1106,15 +1106,17 @@
         <v>17</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="G21" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="H21" s="3"/>
+      <c r="H21" s="3" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="22" spans="1:8" ht="25.5" customHeight="1">
       <c r="A22" s="5" t="s">
@@ -1716,15 +1718,17 @@
         <v>52</v>
       </c>
       <c r="E46" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F46" s="8" t="s">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="G46" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="H46" s="3"/>
+      <c r="H46" s="3" t="s">
+        <v>55</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="4">

--- a/论文处理信息登记表.xlsx
+++ b/论文处理信息登记表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rockie\Desktop\大创\Date Record\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A339671C-CC75-430A-91F0-44874E77AA60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FA66B16-78CB-4D48-8395-CA3926E620C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="451" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="75">
   <si>
     <t>Paper 数据登记表</t>
   </si>
@@ -54,210 +54,234 @@
     <t>paperid</t>
   </si>
   <si>
+    <t>是否复审</t>
+  </si>
+  <si>
+    <t>QA</t>
+  </si>
+  <si>
+    <t>登记人</t>
+  </si>
+  <si>
+    <t>复审人</t>
+  </si>
+  <si>
+    <t>含 PT 数据</t>
+  </si>
+  <si>
+    <t>Aucone_AUG_PPCF_2024</t>
+  </si>
+  <si>
+    <t>是</t>
+  </si>
+  <si>
+    <t>否</t>
+  </si>
+  <si>
+    <t>待复审</t>
+  </si>
+  <si>
+    <t>王澔博</t>
+  </si>
+  <si>
+    <t>含 NT 实验数据</t>
+  </si>
+  <si>
+    <t>Moret_TCV_PRL_1997</t>
+  </si>
+  <si>
+    <t>已复审</t>
+  </si>
+  <si>
+    <t>Merlo_TOKAMAK_PoP_2023</t>
+  </si>
+  <si>
+    <t>Muscente_TCV_NME_2023</t>
+  </si>
+  <si>
+    <t>Nishimura_DIIID_PoP_2020</t>
+  </si>
+  <si>
+    <t>Bagnato_TCV_PPCF_2024</t>
+  </si>
+  <si>
+    <t>Merlo_TCV_PoP_2019</t>
+  </si>
+  <si>
+    <t>Paz-Soldan_DIIID_NF_2024</t>
+  </si>
+  <si>
+    <t>Paz-Soldan_DIIID_PPCF_2021</t>
+  </si>
+  <si>
+    <t>Pochelon_TCV_NF_1999</t>
+  </si>
+  <si>
+    <t>徐逸川</t>
+  </si>
+  <si>
+    <t>Balestri_SMART_PPCF_2024</t>
+  </si>
+  <si>
+    <t>Balestri_MULTI_PPCF_2025</t>
+  </si>
+  <si>
+    <t>Balestri_TCV_PPCF_2024</t>
+  </si>
+  <si>
+    <t>Sauter_DEMO_FED_2016</t>
+  </si>
+  <si>
+    <t>Schwartz_DEMO_NF_2022</t>
+  </si>
+  <si>
+    <t>Sheffield_GENERIC_FST_2016</t>
+  </si>
+  <si>
+    <t>Slendebroek_DIIID_NF_2026</t>
+  </si>
+  <si>
+    <t>Coda_TCV_PPCF_2022</t>
+  </si>
+  <si>
+    <t>Coda_TCV_NF_2019</t>
+  </si>
+  <si>
+    <t>Happel_AUG_NF_2023</t>
+  </si>
+  <si>
+    <t>Ren_ReactorTokamak_PPCF_2016</t>
+  </si>
+  <si>
+    <t>Rewoldt_ISXB_PoF_1982</t>
+  </si>
+  <si>
+    <t>Singh_TOK_NF_2023</t>
+  </si>
+  <si>
+    <t>Rienacker_TCV_NF_2026</t>
+  </si>
+  <si>
+    <t>Scotti_DIII-D_NF_2024</t>
+  </si>
+  <si>
+    <t>Sciortino_DIIID_PPCF_2022</t>
+  </si>
+  <si>
+    <t>Saarelma_DIII-D_PPCF_2021</t>
+  </si>
+  <si>
+    <t>Zheng_Generic_PoP_2025</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>否</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lim_MULTI_PPCF_2023</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>是</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Zhou_EUDEMO_PPCF_2021</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fevrier_TCV_PPCF_2024</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>刘芸琪</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Marinoni_DIII-D_TCV_IAEA-FEC_2020</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Marinoni_MULTI_RMPP_2021</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>徐逸川</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Kikuchi_MULTI_Energies_2014</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Kikuchi_MULTI_EPS_2015</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Kikuchi_MULTI_NF_2019</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Kikuchi_MULTI_JPSConfProc_2014</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Merle_TCV_PPCF_2017</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Kikuchi_SWIP_CONF_2025</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Nelson_REACTOR_NF_2022</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Nelson_MAST-U_NF_2024</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Nelson_DIII-D_ITPAPEP_2025</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>已复审</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Boyes_DIIID_TSDW_2023</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Singh_NA_NF_2022</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>刘芸琪</t>
+  </si>
+  <si>
     <t>是否含 NT 实验数据</t>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>是否含 NT 模拟数据</t>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>是否有 PT 数据</t>
-  </si>
-  <si>
-    <t>是否复审</t>
-  </si>
-  <si>
-    <t>QA</t>
-  </si>
-  <si>
-    <t>登记人</t>
-  </si>
-  <si>
-    <t>复审人</t>
-  </si>
-  <si>
-    <t>含 PT 数据</t>
-  </si>
-  <si>
-    <t>Aucone_AUG_PPCF_2024</t>
-  </si>
-  <si>
-    <t>是</t>
-  </si>
-  <si>
-    <t>否</t>
-  </si>
-  <si>
-    <t>待复审</t>
-  </si>
-  <si>
-    <t>王澔博</t>
-  </si>
-  <si>
-    <t>含 NT 实验数据</t>
-  </si>
-  <si>
-    <t>Moret_TCV_PRL_1997</t>
-  </si>
-  <si>
-    <t>已复审</t>
-  </si>
-  <si>
-    <t>Merlo_TOKAMAK_PoP_2023</t>
-  </si>
-  <si>
-    <t>Muscente_TCV_NME_2023</t>
-  </si>
-  <si>
-    <t>Nishimura_DIIID_PoP_2020</t>
-  </si>
-  <si>
-    <t>Bagnato_TCV_PPCF_2024</t>
-  </si>
-  <si>
-    <t>Merlo_TCV_PoP_2019</t>
-  </si>
-  <si>
-    <t>Paz-Soldan_DIIID_NF_2024</t>
-  </si>
-  <si>
-    <t>Paz-Soldan_DIIID_PPCF_2021</t>
-  </si>
-  <si>
-    <t>Pochelon_TCV_NF_1999</t>
-  </si>
-  <si>
-    <t>徐逸川</t>
-  </si>
-  <si>
-    <t>Balestri_SMART_PPCF_2024</t>
-  </si>
-  <si>
-    <t>Balestri_MULTI_PPCF_2025</t>
-  </si>
-  <si>
-    <t>Balestri_TCV_PPCF_2024</t>
-  </si>
-  <si>
-    <t>Sauter_DEMO_FED_2016</t>
-  </si>
-  <si>
-    <t>Schwartz_DEMO_NF_2022</t>
-  </si>
-  <si>
-    <t>Sheffield_GENERIC_FST_2016</t>
-  </si>
-  <si>
-    <t>Slendebroek_DIIID_NF_2026</t>
-  </si>
-  <si>
-    <t>Coda_TCV_PPCF_2022</t>
-  </si>
-  <si>
-    <t>Coda_TCV_NF_2019</t>
-  </si>
-  <si>
-    <t>Happel_AUG_NF_2023</t>
-  </si>
-  <si>
-    <t>Ren_ReactorTokamak_PPCF_2016</t>
-  </si>
-  <si>
-    <t>Rewoldt_ISXB_PoF_1982</t>
-  </si>
-  <si>
-    <t>Singh_TOK_NF_2023</t>
-  </si>
-  <si>
-    <t>Rienacker_TCV_NF_2026</t>
-  </si>
-  <si>
-    <t>Scotti_DIII-D_NF_2024</t>
-  </si>
-  <si>
-    <t>Sciortino_DIIID_PPCF_2022</t>
-  </si>
-  <si>
-    <t>Saarelma_DIII-D_PPCF_2021</t>
-  </si>
-  <si>
-    <t>Zheng_Generic_PoP_2025</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>否</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Lim_MULTI_PPCF_2023</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>是</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Zhou_EUDEMO_PPCF_2021</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Fevrier_TCV_PPCF_2024</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>刘芸琪</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Marinoni_DIII-D_TCV_IAEA-FEC_2020</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Marinoni_MULTI_RMPP_2021</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>徐逸川</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Kikuchi_MULTI_Energies_2014</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Kikuchi_MULTI_EPS_2015</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Kikuchi_MULTI_NF_2019</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Kikuchi_MULTI_JPSConfProc_2014</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Merle_TCV_PPCF_2017</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Kikuchi_SWIP_CONF_2025</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Nelson_REACTOR_NF_2022</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Nelson_MAST-U_NF_2024</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Nelson_DIII-D_ITPAPEP_2025</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>已复审</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Song_DIIID_NF_2021</t>
+  </si>
+  <si>
+    <t>是(模拟)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Yu_DIIID_PoP_2023</t>
   </si>
 </sst>
 </file>
@@ -587,7 +611,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K46"/>
+  <dimension ref="A1:K50"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="42.453125" customWidth="1"/>
@@ -659,28 +683,28 @@
         <v>6</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="F4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="G4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="H4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="J4" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>14</v>
       </c>
       <c r="K4" s="1">
         <v>11</v>
@@ -688,31 +712,31 @@
     </row>
     <row r="5" spans="1:11" ht="25.5" customHeight="1">
       <c r="A5" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E5" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="F5" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>55</v>
-      </c>
       <c r="J5" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="K5" s="1">
         <v>14</v>
@@ -720,29 +744,29 @@
     </row>
     <row r="6" spans="1:11" ht="25.5" customHeight="1">
       <c r="A6" s="5" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H6" s="3"/>
       <c r="J6" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="K6" s="1">
         <v>12</v>
@@ -750,985 +774,1081 @@
     </row>
     <row r="7" spans="1:11" ht="25.5" customHeight="1">
       <c r="A7" s="5" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H7" s="3"/>
     </row>
     <row r="8" spans="1:11" ht="25.5" customHeight="1">
       <c r="A8" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E8" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H8" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="25.5" customHeight="1">
       <c r="A9" s="5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H9" s="3"/>
     </row>
     <row r="10" spans="1:11" ht="25.5" customHeight="1">
       <c r="A10" s="5" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E10" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H10" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="25.5" customHeight="1">
       <c r="A11" s="5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E11" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H11" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="25.5" customHeight="1">
       <c r="A12" s="5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H12" s="3"/>
     </row>
     <row r="13" spans="1:11" ht="25.5" customHeight="1">
       <c r="A13" s="5" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H13" s="3"/>
     </row>
     <row r="14" spans="1:11" ht="25.5" customHeight="1">
       <c r="A14" s="5" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H14" s="3"/>
     </row>
     <row r="15" spans="1:11" ht="25.5" customHeight="1">
       <c r="A15" s="5" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H15" s="3"/>
     </row>
     <row r="16" spans="1:11" ht="25.5" customHeight="1">
       <c r="A16" s="5" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H16" s="3"/>
     </row>
     <row r="17" spans="1:8" ht="25.5" customHeight="1">
       <c r="A17" s="5" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E17" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H17" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="F17" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="G17" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="25.5" customHeight="1">
       <c r="A18" s="5" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H18" s="3"/>
     </row>
     <row r="19" spans="1:8" ht="25.5" customHeight="1">
       <c r="A19" s="5" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H19" s="3"/>
     </row>
     <row r="20" spans="1:8" ht="25.5" customHeight="1">
       <c r="A20" s="5" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H20" s="3"/>
     </row>
     <row r="21" spans="1:8" ht="25.5" customHeight="1">
       <c r="A21" s="5" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E21" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H21" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="F21" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="25.5" customHeight="1">
       <c r="A22" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H22" s="3"/>
     </row>
     <row r="23" spans="1:8" ht="25.5" customHeight="1">
       <c r="A23" s="5" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H23" s="3"/>
     </row>
     <row r="24" spans="1:8" ht="25.5" customHeight="1">
       <c r="A24" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E24" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H24" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="F24" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="G24" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="25.5" customHeight="1">
       <c r="A25" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H25" s="3"/>
     </row>
     <row r="26" spans="1:8" ht="25.5" customHeight="1">
       <c r="A26" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H26" s="3"/>
     </row>
     <row r="27" spans="1:8" ht="25.5" customHeight="1">
       <c r="A27" s="5" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H27" s="3"/>
     </row>
     <row r="28" spans="1:8" ht="25.5" customHeight="1">
       <c r="A28" s="5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E28" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="G28" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H28" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="F28" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="G28" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="25.5" customHeight="1">
       <c r="A29" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H29" s="3"/>
     </row>
     <row r="30" spans="1:8" ht="25.5" customHeight="1">
       <c r="A30" s="5" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E30" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="F30" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="G30" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H30" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="F30" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="G30" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="25.5" customHeight="1">
       <c r="A31" s="5" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E31" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="F31" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="G31" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H31" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="F31" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="G31" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="25.5" customHeight="1">
       <c r="A32" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H32" s="3"/>
     </row>
     <row r="33" spans="1:8" ht="25.5" customHeight="1">
       <c r="A33" s="5" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H33" s="3"/>
     </row>
     <row r="34" spans="1:8" ht="25.5" customHeight="1">
       <c r="A34" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H34" s="3"/>
     </row>
     <row r="35" spans="1:8" ht="25.5" customHeight="1">
       <c r="A35" s="5" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B35" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F35" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G35" s="5" t="s">
         <v>52</v>
-      </c>
-      <c r="C35" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="D35" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="E35" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F35" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="G35" s="5" t="s">
-        <v>55</v>
       </c>
       <c r="H35" s="3"/>
     </row>
     <row r="36" spans="1:8" ht="25.5" customHeight="1">
       <c r="A36" s="5" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="H36" s="3"/>
     </row>
     <row r="37" spans="1:8" ht="25.5" customHeight="1">
       <c r="A37" s="5" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="H37" s="3"/>
     </row>
     <row r="38" spans="1:8" ht="25.5" customHeight="1">
       <c r="A38" s="5" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="H38" s="3"/>
     </row>
     <row r="39" spans="1:8" ht="25.5" customHeight="1">
       <c r="A39" s="5" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="H39" s="3"/>
     </row>
     <row r="40" spans="1:8" ht="25.5" customHeight="1">
       <c r="A40" s="5" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="H40" s="3"/>
     </row>
     <row r="41" spans="1:8" ht="25.5" customHeight="1">
       <c r="A41" s="5" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F41" s="8" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="H41" s="3"/>
     </row>
     <row r="42" spans="1:8" ht="25.5" customHeight="1">
       <c r="A42" s="5" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B42" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="E42" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="F42" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="G42" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="H42" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="C42" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="D42" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="E42" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="F42" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="G42" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="25.5" customHeight="1">
       <c r="A43" s="5" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F43" s="8" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="H43" s="3"/>
     </row>
     <row r="44" spans="1:8" ht="25.5" customHeight="1">
       <c r="A44" s="5" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F44" s="8" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="H44" s="3"/>
     </row>
     <row r="45" spans="1:8" ht="25.5" customHeight="1">
       <c r="A45" s="5" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F45" s="8" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="H45" s="3"/>
     </row>
     <row r="46" spans="1:8" ht="25.5" customHeight="1">
       <c r="A46" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="E46" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="F46" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="G46" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="14.5">
+      <c r="A47" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="E47" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F47" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="H47" s="3"/>
+    </row>
+    <row r="48" spans="1:8" ht="14.5">
+      <c r="A48" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B46" s="6" t="s">
+      <c r="B48" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="D48" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="E48" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F48" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G48" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C46" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="D46" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="E46" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="F46" s="8" t="s">
+      <c r="H48" s="3"/>
+    </row>
+    <row r="49" spans="1:8" ht="14.5">
+      <c r="A49" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="D49" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="E49" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F49" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G49" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="G46" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>55</v>
-      </c>
+      <c r="H49" s="3"/>
+    </row>
+    <row r="50" spans="1:8" ht="14.5">
+      <c r="A50" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C50" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E50" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F50" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="H50" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="4">
